--- a/data/trans_orig/P1201-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1201-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según frecuencia de sentirse calmado y tranquilo en 2007</t>
+          <t>Población según frecuencia de sentirse calmado y tranquilo en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10590</t>
+          <t>10225</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22233</t>
+          <t>22203</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10729</t>
+          <t>10768</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27525</t>
+          <t>27568</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32393</t>
+          <t>31906</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57668</t>
+          <t>58545</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54969</t>
+          <t>53671</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87302</t>
+          <t>86026</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94340</t>
+          <t>93665</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>134424</t>
+          <t>133774</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>163610</t>
+          <t>165785</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>214559</t>
+          <t>215367</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>245566</t>
+          <t>248148</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>305647</t>
+          <t>305790</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>430187</t>
+          <t>427011</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>510815</t>
+          <t>504654</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>104209</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>146546</t>
+          <t>143558</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>202243</t>
+          <t>202802</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>254738</t>
+          <t>254544</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>314977</t>
+          <t>316066</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>380811</t>
+          <t>388497</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359147</t>
+          <t>361431</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>420476</t>
+          <t>423025</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>466929</t>
+          <t>465538</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>535578</t>
+          <t>533029</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>843547</t>
+          <t>842164</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>938178</t>
+          <t>936743</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,92%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>253044</t>
+          <t>251190</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>311452</t>
+          <t>307743</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>203685</t>
+          <t>205981</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>260211</t>
+          <t>261411</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>471499</t>
+          <t>474378</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>552847</t>
+          <t>551476</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28206</t>
+          <t>26964</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18596</t>
+          <t>18404</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40527</t>
+          <t>39917</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>31219</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59524</t>
+          <t>60453</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32629</t>
+          <t>31311</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58140</t>
+          <t>58507</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58548</t>
+          <t>61461</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>92213</t>
+          <t>93593</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>96509</t>
+          <t>97447</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>138891</t>
+          <t>140018</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>171404</t>
+          <t>172905</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>225033</t>
+          <t>222975</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>219833</t>
+          <t>216340</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>278278</t>
+          <t>274238</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>408026</t>
+          <t>409189</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>488084</t>
+          <t>485368</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197329</t>
+          <t>197441</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>251884</t>
+          <t>252925</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>263104</t>
+          <t>264872</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>324211</t>
+          <t>327408</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>471764</t>
+          <t>478094</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>556006</t>
+          <t>557168</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,98%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>738033</t>
+          <t>737708</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>822845</t>
+          <t>822801</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>596529</t>
+          <t>592187</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>673116</t>
+          <t>673819</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1354476</t>
+          <t>1355050</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1476926</t>
+          <t>1470748</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,83%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>394721</t>
+          <t>398574</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>470011</t>
+          <t>472566</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>280493</t>
+          <t>281389</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>344225</t>
+          <t>345933</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>694944</t>
+          <t>692411</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>793954</t>
+          <t>794238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>889</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>7762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16476</t>
+          <t>17470</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21662</t>
+          <t>20893</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9540</t>
+          <t>8991</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25141</t>
+          <t>25897</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12850</t>
+          <t>12645</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30919</t>
+          <t>31045</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26547</t>
+          <t>26704</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50529</t>
+          <t>50226</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49294</t>
+          <t>50956</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>80489</t>
+          <t>81997</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55593</t>
+          <t>56417</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>86828</t>
+          <t>87275</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>114596</t>
+          <t>114603</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>159111</t>
+          <t>159023</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>56753</t>
+          <t>56009</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>88033</t>
+          <t>87668</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>58353</t>
+          <t>56607</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>89855</t>
+          <t>88259</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>120684</t>
+          <t>120404</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>166431</t>
+          <t>166481</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>208312</t>
+          <t>206560</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>256800</t>
+          <t>257010</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>185435</t>
+          <t>183950</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>228896</t>
+          <t>228503</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>406014</t>
+          <t>402675</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>472057</t>
+          <t>471568</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,88%</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>141810</t>
+          <t>141990</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>186125</t>
+          <t>187039</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>80345</t>
+          <t>80904</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>114601</t>
+          <t>116196</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>230508</t>
+          <t>233257</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>287626</t>
+          <t>291428</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14763</t>
+          <t>14756</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36806</t>
+          <t>35502</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,42 +3138,42 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>50577</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>37982</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>67272</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>50577</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>38089</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>65580</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>57414</t>
+          <t>57798</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>92499</t>
+          <t>94372</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>84281</t>
+          <t>85030</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>123373</t>
+          <t>123660</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>138309</t>
+          <t>139606</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>189680</t>
+          <t>187378</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>236738</t>
+          <t>234413</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>299534</t>
+          <t>301087</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>412794</t>
+          <t>413626</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>490270</t>
+          <t>492602</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>547334</t>
+          <t>551631</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>638229</t>
+          <t>638438</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>984436</t>
+          <t>981818</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1105183</t>
+          <t>1102515</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>381346</t>
+          <t>382286</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>455613</t>
+          <t>457304</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>545272</t>
+          <t>546365</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>636847</t>
+          <t>642511</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>947182</t>
+          <t>951250</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1066084</t>
+          <t>1069072</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1348870</t>
+          <t>1349338</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1462878</t>
+          <t>1457244</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1276435</t>
+          <t>1275237</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1399176</t>
+          <t>1396899</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2663804</t>
+          <t>2662085</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2823914</t>
+          <t>2830429</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,53%</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>825648</t>
+          <t>826475</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>930515</t>
+          <t>928769</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>597762</t>
+          <t>594322</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>688071</t>
+          <t>688455</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1445445</t>
+          <t>1447643</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1589232</t>
+          <t>1591764</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3949,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según frecuencia de sentirse calmado y tranquilo en 2012</t>
+          <t>Población según frecuencia de sentirse calmado y tranquilo en 2012 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15748</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36284</t>
+          <t>37759</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43810</t>
+          <t>42970</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73800</t>
+          <t>76247</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66974</t>
+          <t>63783</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103531</t>
+          <t>101365</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32820</t>
+          <t>31465</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59896</t>
+          <t>57746</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60281</t>
+          <t>62470</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>96498</t>
+          <t>97191</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99850</t>
+          <t>100662</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>143670</t>
+          <t>143961</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>116264</t>
+          <t>116906</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>161108</t>
+          <t>161656</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>312472</t>
+          <t>313787</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>379573</t>
+          <t>381607</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>445196</t>
+          <t>443477</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>522548</t>
+          <t>525564</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>104031</t>
+          <t>103191</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144602</t>
+          <t>149656</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>138819</t>
+          <t>136116</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>183793</t>
+          <t>184348</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>251728</t>
+          <t>252855</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>313488</t>
+          <t>316982</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4596,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>263427</t>
+          <t>265510</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>324511</t>
+          <t>326628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>377552</t>
+          <t>375746</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>446752</t>
+          <t>443287</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>664910</t>
+          <t>661253</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>753783</t>
+          <t>749892</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,48%</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>315991</t>
+          <t>316112</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>377512</t>
+          <t>378885</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255410</t>
+          <t>254673</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>319695</t>
+          <t>314565</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>584840</t>
+          <t>584548</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>671975</t>
+          <t>676790</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27039</t>
+          <t>28046</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51684</t>
+          <t>52105</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50431</t>
+          <t>51433</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>84779</t>
+          <t>85403</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85290</t>
+          <t>86696</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>125725</t>
+          <t>129667</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34324</t>
+          <t>36266</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62670</t>
+          <t>61593</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52523</t>
+          <t>53136</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>84773</t>
+          <t>87655</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>96370</t>
+          <t>94934</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>141088</t>
+          <t>137118</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>218039</t>
+          <t>215270</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>274656</t>
+          <t>277964</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>319185</t>
+          <t>319039</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>390379</t>
+          <t>391803</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>554442</t>
+          <t>553882</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>645808</t>
+          <t>643753</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>225623</t>
+          <t>220390</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>288886</t>
+          <t>283532</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>222827</t>
+          <t>222817</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>283056</t>
+          <t>281381</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>459168</t>
+          <t>464500</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>548431</t>
+          <t>548799</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>596306</t>
+          <t>594889</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>683566</t>
+          <t>682977</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>422949</t>
+          <t>424268</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>497051</t>
+          <t>499630</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1048370</t>
+          <t>1046696</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1154494</t>
+          <t>1164655</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>692808</t>
+          <t>697762</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>779587</t>
+          <t>785125</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>518998</t>
+          <t>517583</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>600484</t>
+          <t>597738</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1231689</t>
+          <t>1235050</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1349790</t>
+          <t>1353667</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2076</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11868</t>
+          <t>12988</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6229</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>21550</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>10753</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29141</t>
+          <t>27473</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2388</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17479</t>
+          <t>18352</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9569</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27099</t>
+          <t>27840</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15906</t>
+          <t>15555</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38596</t>
+          <t>37475</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5960,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42040</t>
+          <t>41610</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>73594</t>
+          <t>72668</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44411</t>
+          <t>44866</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73615</t>
+          <t>73862</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>93665</t>
+          <t>94349</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>137393</t>
+          <t>136737</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>56422</t>
+          <t>55954</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>91821</t>
+          <t>90122</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>42383</t>
+          <t>42907</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72071</t>
+          <t>71251</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>105956</t>
+          <t>105220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>151096</t>
+          <t>149674</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>124916</t>
+          <t>127247</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>168543</t>
+          <t>171980</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>133218</t>
+          <t>132819</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>176870</t>
+          <t>173179</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>269243</t>
+          <t>271873</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>330678</t>
+          <t>332243</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>170744</t>
+          <t>170112</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>215349</t>
+          <t>215425</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>139331</t>
+          <t>140387</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>182583</t>
+          <t>183784</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>321744</t>
+          <t>325007</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>385714</t>
+          <t>386400</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,16%</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54168</t>
+          <t>55085</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>87183</t>
+          <t>88952</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>113645</t>
+          <t>112329</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>160344</t>
+          <t>161229</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>176554</t>
+          <t>178239</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>235877</t>
+          <t>233845</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>79513</t>
+          <t>81563</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>122915</t>
+          <t>122182</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>138786</t>
+          <t>137850</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>190664</t>
+          <t>187733</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>228764</t>
+          <t>231020</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>296110</t>
+          <t>295430</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>396418</t>
+          <t>400189</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>482738</t>
+          <t>485059</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>708992</t>
+          <t>702754</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>810805</t>
+          <t>810532</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1126942</t>
+          <t>1138913</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1258523</t>
+          <t>1264390</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>403588</t>
+          <t>409383</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>486784</t>
+          <t>488368</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>423712</t>
+          <t>424021</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>504905</t>
+          <t>510971</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>857673</t>
+          <t>858209</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>979374</t>
+          <t>973693</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1025977</t>
+          <t>1027154</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1139225</t>
+          <t>1139441</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>969413</t>
+          <t>970165</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1080656</t>
+          <t>1075466</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2024795</t>
+          <t>2028316</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2194595</t>
+          <t>2181781</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1220944</t>
+          <t>1213536</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1337084</t>
+          <t>1336695</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>946619</t>
+          <t>947633</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1053678</t>
+          <t>1057332</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2197359</t>
+          <t>2189128</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2358627</t>
+          <t>2353710</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7360,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según frecuencia de sentirse calmado y tranquilo en 2016</t>
+          <t>Población según frecuencia de sentirse calmado y tranquilo en 2016 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17509</t>
+          <t>17345</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21398</t>
+          <t>21529</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43769</t>
+          <t>45998</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29833</t>
+          <t>30196</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55456</t>
+          <t>55736</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -7668,12 +7668,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15643</t>
+          <t>16215</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34010</t>
+          <t>35050</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7683,12 +7683,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41057</t>
+          <t>42138</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72082</t>
+          <t>73146</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61851</t>
+          <t>61236</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98925</t>
+          <t>97948</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -7781,12 +7781,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100478</t>
+          <t>101751</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>141140</t>
+          <t>142134</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>169352</t>
+          <t>170264</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>223612</t>
+          <t>223579</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>282800</t>
+          <t>285719</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>346446</t>
+          <t>349743</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -7894,12 +7894,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>134896</t>
+          <t>135885</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>178899</t>
+          <t>178589</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7929,12 +7929,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>198562</t>
+          <t>196291</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>253813</t>
+          <t>252616</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7964,12 +7964,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>346089</t>
+          <t>349295</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>415909</t>
+          <t>418469</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>200321</t>
+          <t>201127</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>249338</t>
+          <t>248095</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8022,12 +8022,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>235647</t>
+          <t>233219</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>293986</t>
+          <t>294390</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>447236</t>
+          <t>448765</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>524484</t>
+          <t>522586</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -8120,12 +8120,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>196443</t>
+          <t>197720</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>245022</t>
+          <t>245770</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>196702</t>
+          <t>197526</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>251922</t>
+          <t>251540</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>407866</t>
+          <t>403968</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>481693</t>
+          <t>479437</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,45%</t>
         </is>
       </c>
     </row>
@@ -8350,12 +8350,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17492</t>
+          <t>17157</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39936</t>
+          <t>38778</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8385,12 +8385,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29473</t>
+          <t>31083</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55291</t>
+          <t>55850</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52785</t>
+          <t>53524</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86548</t>
+          <t>87815</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -8463,12 +8463,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17113</t>
+          <t>17219</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>39485</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38884</t>
+          <t>39175</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66785</t>
+          <t>67465</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>60469</t>
+          <t>60222</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>95042</t>
+          <t>97129</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -8576,12 +8576,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>150037</t>
+          <t>147882</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>202357</t>
+          <t>199892</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>185030</t>
+          <t>183498</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>240366</t>
+          <t>236576</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>349293</t>
+          <t>346232</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>422293</t>
+          <t>421790</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -8689,12 +8689,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>264597</t>
+          <t>268707</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>333916</t>
+          <t>332324</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>291394</t>
+          <t>293191</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>357478</t>
+          <t>359932</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>576110</t>
+          <t>577003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>668883</t>
+          <t>672889</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>652365</t>
+          <t>651859</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>738679</t>
+          <t>738114</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>591378</t>
+          <t>588612</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>670916</t>
+          <t>675195</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8852,12 +8852,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1265472</t>
+          <t>1259810</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1388822</t>
+          <t>1382427</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8887,12 +8887,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>
@@ -8915,12 +8915,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>809669</t>
+          <t>814062</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>904993</t>
+          <t>906591</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8930,12 +8930,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8950,12 +8950,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>686236</t>
+          <t>680867</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>776635</t>
+          <t>772045</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1521678</t>
+          <t>1528875</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1649715</t>
+          <t>1649012</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9000,12 +9000,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -9145,12 +9145,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>8407</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>10021</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15071</t>
+          <t>14449</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -9258,12 +9258,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17371</t>
+          <t>17390</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19682</t>
+          <t>19679</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10885</t>
+          <t>11756</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30467</t>
+          <t>32901</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -9371,12 +9371,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29104</t>
+          <t>29784</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56012</t>
+          <t>56099</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9386,12 +9386,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51211</t>
+          <t>50867</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>81912</t>
+          <t>80298</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9421,12 +9421,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86659</t>
+          <t>86844</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>126188</t>
+          <t>125293</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -9484,12 +9484,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55365</t>
+          <t>58163</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>88804</t>
+          <t>89495</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9499,12 +9499,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>71203</t>
+          <t>70487</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>105269</t>
+          <t>105159</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9534,12 +9534,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9554,12 +9554,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>136681</t>
+          <t>137907</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>181904</t>
+          <t>185637</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9569,12 +9569,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>170039</t>
+          <t>169780</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>217983</t>
+          <t>215872</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>166493</t>
+          <t>166081</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>212654</t>
+          <t>210966</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9647,12 +9647,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>349272</t>
+          <t>349362</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>414703</t>
+          <t>415058</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,94%</t>
         </is>
       </c>
     </row>
@@ -9710,12 +9710,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>204392</t>
+          <t>205430</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>253306</t>
+          <t>253210</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9725,12 +9725,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>170633</t>
+          <t>171205</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>216356</t>
+          <t>216684</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>389935</t>
+          <t>390118</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>456294</t>
+          <t>452027</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,32%</t>
         </is>
       </c>
     </row>
@@ -9940,12 +9940,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27631</t>
+          <t>27891</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53969</t>
+          <t>52665</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9955,12 +9955,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59834</t>
+          <t>60067</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>97102</t>
+          <t>96976</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>95574</t>
+          <t>97015</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>137865</t>
+          <t>144072</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -10053,12 +10053,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>45804</t>
+          <t>45157</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>78037</t>
+          <t>77256</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>95549</t>
+          <t>99063</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>140311</t>
+          <t>142588</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>150468</t>
+          <t>151438</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>205121</t>
+          <t>208060</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -10166,12 +10166,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>296855</t>
+          <t>298438</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>371492</t>
+          <t>368128</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10181,12 +10181,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>433794</t>
+          <t>430359</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>513153</t>
+          <t>513290</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10216,12 +10216,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>748147</t>
+          <t>754042</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>860159</t>
+          <t>859417</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -10279,12 +10279,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>484123</t>
+          <t>485455</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>570608</t>
+          <t>570468</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>592863</t>
+          <t>590072</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>683942</t>
+          <t>686335</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10329,12 +10329,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1104682</t>
+          <t>1097735</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1236796</t>
+          <t>1224204</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1051503</t>
+          <t>1051154</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1157106</t>
+          <t>1164201</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1021948</t>
+          <t>1025659</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1137036</t>
+          <t>1132216</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10442,12 +10442,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2111143</t>
+          <t>2117904</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2267550</t>
+          <t>2273673</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,94%</t>
         </is>
       </c>
     </row>
@@ -10505,12 +10505,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1245921</t>
+          <t>1245768</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1360437</t>
+          <t>1361592</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10540,12 +10540,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1088285</t>
+          <t>1088863</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1203644</t>
+          <t>1204990</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10555,12 +10555,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10575,12 +10575,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2370123</t>
+          <t>2373543</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2527406</t>
+          <t>2531576</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10590,12 +10590,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -10771,7 +10771,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según frecuencia de sentirse calmado y tranquilo en 2023</t>
+          <t>Población según frecuencia de sentirse calmado y tranquilo en 2023 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10966,12 +10966,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15786</t>
+          <t>15547</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10981,12 +10981,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11001,12 +11001,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13244</t>
+          <t>12641</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25651</t>
+          <t>24578</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11036,12 +11036,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20344</t>
+          <t>20155</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35733</t>
+          <t>35228</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -11079,12 +11079,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15852</t>
+          <t>15530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34862</t>
+          <t>33822</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11094,12 +11094,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11114,12 +11114,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48989</t>
+          <t>49975</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72862</t>
+          <t>71798</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11129,12 +11129,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11149,12 +11149,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69832</t>
+          <t>68998</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99785</t>
+          <t>98119</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11164,12 +11164,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -11192,12 +11192,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56396</t>
+          <t>56215</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>82822</t>
+          <t>83145</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11207,12 +11207,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>122807</t>
+          <t>123006</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>155380</t>
+          <t>154095</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11242,47 +11242,47 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
+          <t>16,28%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>20,4%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>206325</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>184187</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>226365</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
           <t>16,25%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>20,57%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>368</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>206325</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>186924</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>230240</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>16,25%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -11305,12 +11305,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82706</t>
+          <t>81241</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115241</t>
+          <t>115361</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>134641</t>
+          <t>133639</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>167225</t>
+          <t>165781</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11355,12 +11355,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11375,12 +11375,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>223366</t>
+          <t>224430</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>273493</t>
+          <t>268620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11390,12 +11390,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -11418,12 +11418,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>139019</t>
+          <t>139039</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>177489</t>
+          <t>178821</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11453,12 +11453,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>194243</t>
+          <t>193029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>234802</t>
+          <t>232532</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11468,12 +11468,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11488,12 +11488,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>343317</t>
+          <t>342955</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>397798</t>
+          <t>395862</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11503,12 +11503,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -11531,12 +11531,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>140058</t>
+          <t>140754</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>178829</t>
+          <t>177867</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11566,12 +11566,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>160305</t>
+          <t>159507</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>198079</t>
+          <t>198221</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11601,12 +11601,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>310489</t>
+          <t>310273</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>364504</t>
+          <t>363241</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11616,12 +11616,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -11761,12 +11761,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10158</t>
+          <t>10257</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>29009</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11796,12 +11796,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25718</t>
+          <t>26160</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53420</t>
+          <t>55928</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11811,12 +11811,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40391</t>
+          <t>40791</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73058</t>
+          <t>76326</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11846,12 +11846,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -11874,12 +11874,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43623</t>
+          <t>40325</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>87167</t>
+          <t>85956</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11909,12 +11909,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>85037</t>
+          <t>87233</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>852212</t>
+          <t>756755</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11924,12 +11924,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11944,12 +11944,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>146743</t>
+          <t>145962</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1018467</t>
+          <t>1015459</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11959,12 +11959,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -11987,12 +11987,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>131857</t>
+          <t>133778</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>230591</t>
+          <t>230777</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12022,12 +12022,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>185581</t>
+          <t>192589</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>297657</t>
+          <t>302877</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12037,12 +12037,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>369191</t>
+          <t>366878</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>511681</t>
+          <t>512160</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12072,12 +12072,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -12100,12 +12100,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>172484</t>
+          <t>159656</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>282744</t>
+          <t>280452</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12115,12 +12115,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12135,12 +12135,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>174667</t>
+          <t>175777</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>277201</t>
+          <t>272938</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12150,12 +12150,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12170,12 +12170,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>376879</t>
+          <t>382838</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>535071</t>
+          <t>539484</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12185,12 +12185,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -12213,12 +12213,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>457856</t>
+          <t>449464</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>742412</t>
+          <t>741189</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12228,12 +12228,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12248,12 +12248,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>415003</t>
+          <t>439376</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>674928</t>
+          <t>674173</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12263,12 +12263,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12283,12 +12283,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>987059</t>
+          <t>996582</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1376405</t>
+          <t>1379334</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12298,12 +12298,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -12326,12 +12326,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>974985</t>
+          <t>972119</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1474357</t>
+          <t>1516393</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12361,12 +12361,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>631006</t>
+          <t>624583</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>981911</t>
+          <t>969742</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1708054</t>
+          <t>1716156</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2368949</t>
+          <t>2400045</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>53,01%</t>
         </is>
       </c>
     </row>
@@ -12556,12 +12556,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14157</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12591,12 +12591,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7177</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18649</t>
+          <t>18241</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12606,12 +12606,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12626,12 +12626,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11402</t>
+          <t>11623</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27444</t>
+          <t>27882</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12641,12 +12641,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -12669,12 +12669,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10087</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28980</t>
+          <t>29764</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12684,12 +12684,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12704,12 +12704,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18284</t>
+          <t>18430</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34316</t>
+          <t>35740</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12719,12 +12719,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12739,12 +12739,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32276</t>
+          <t>32931</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56178</t>
+          <t>55767</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -12782,12 +12782,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51882</t>
+          <t>52277</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83297</t>
+          <t>85741</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12797,12 +12797,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12817,12 +12817,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>75648</t>
+          <t>75049</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>107092</t>
+          <t>106913</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12832,12 +12832,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12852,12 +12852,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>136003</t>
+          <t>135358</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>180598</t>
+          <t>180893</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12867,12 +12867,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -12895,12 +12895,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>63648</t>
+          <t>61929</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>98452</t>
+          <t>97227</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12910,12 +12910,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>73188</t>
+          <t>74479</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>102133</t>
+          <t>105583</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12945,12 +12945,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12965,12 +12965,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>144948</t>
+          <t>143578</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>187403</t>
+          <t>189929</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12980,12 +12980,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -13008,12 +13008,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>169217</t>
+          <t>170315</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>221722</t>
+          <t>218751</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13023,12 +13023,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13043,12 +13043,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>204310</t>
+          <t>205557</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>249005</t>
+          <t>247556</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13078,12 +13078,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>391013</t>
+          <t>391681</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>455732</t>
+          <t>457762</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,02%</t>
         </is>
       </c>
     </row>
@@ -13121,12 +13121,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>252527</t>
+          <t>253746</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>311983</t>
+          <t>310614</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13136,12 +13136,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>198590</t>
+          <t>198055</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>244283</t>
+          <t>243449</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13191,12 +13191,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>465862</t>
+          <t>464078</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>540988</t>
+          <t>537464</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,12%</t>
         </is>
       </c>
     </row>
@@ -13351,12 +13351,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22506</t>
+          <t>22781</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47472</t>
+          <t>47843</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13386,12 +13386,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52599</t>
+          <t>52557</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>85916</t>
+          <t>84639</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13421,12 +13421,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>82595</t>
+          <t>83651</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>125024</t>
+          <t>125149</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -13464,12 +13464,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>79040</t>
+          <t>79241</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>133294</t>
+          <t>129514</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13479,12 +13479,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13499,12 +13499,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>171436</t>
+          <t>172812</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1093120</t>
+          <t>971288</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13514,12 +13514,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13534,12 +13534,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>272993</t>
+          <t>267170</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1433287</t>
+          <t>1195274</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13549,12 +13549,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>257894</t>
+          <t>247485</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>372656</t>
+          <t>372629</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -13612,12 +13612,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>380226</t>
+          <t>393394</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>534068</t>
+          <t>534154</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13627,7 +13627,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -13647,12 +13647,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>706031</t>
+          <t>712668</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>885070</t>
+          <t>879586</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13662,12 +13662,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -13690,12 +13690,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>318166</t>
+          <t>322849</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>468532</t>
+          <t>463268</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13705,12 +13705,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13725,12 +13725,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>386276</t>
+          <t>392059</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>521310</t>
+          <t>520655</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13760,12 +13760,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>766385</t>
+          <t>765639</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>961925</t>
+          <t>958082</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -13803,12 +13803,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>772688</t>
+          <t>750998</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1094774</t>
+          <t>1096088</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13818,12 +13818,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>830181</t>
+          <t>842125</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1113426</t>
+          <t>1112819</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13873,12 +13873,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1764944</t>
+          <t>1754197</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2180879</t>
+          <t>2168179</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -13916,12 +13916,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1409050</t>
+          <t>1410324</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2031180</t>
+          <t>2051162</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13931,12 +13931,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1019892</t>
+          <t>1043009</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1380623</t>
+          <t>1376010</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13986,12 +13986,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2538948</t>
+          <t>2551513</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3278298</t>
+          <t>3254462</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>45,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1201-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1201-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>10233</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7292</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22203</t>
+          <t>23053</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10768</t>
+          <t>11645</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27568</t>
+          <t>27427</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31906</t>
+          <t>31367</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58545</t>
+          <t>56938</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53671</t>
+          <t>54954</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86026</t>
+          <t>87772</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>93665</t>
+          <t>93341</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>133774</t>
+          <t>132752</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>165785</t>
+          <t>165891</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>215367</t>
+          <t>215499</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>248148</t>
+          <t>247649</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>305790</t>
+          <t>305711</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>427011</t>
+          <t>427110</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>504654</t>
+          <t>504422</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>104715</t>
+          <t>103201</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143558</t>
+          <t>144058</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>202802</t>
+          <t>203338</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>254544</t>
+          <t>256215</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>316066</t>
+          <t>317122</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>388497</t>
+          <t>387231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>361431</t>
+          <t>360985</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423025</t>
+          <t>420019</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>465538</t>
+          <t>462617</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>533029</t>
+          <t>531008</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>842164</t>
+          <t>843957</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>936743</t>
+          <t>937737</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,96%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>251190</t>
+          <t>254566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>307743</t>
+          <t>312131</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>205981</t>
+          <t>207045</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>261411</t>
+          <t>263332</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>474378</t>
+          <t>472834</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>551476</t>
+          <t>554756</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26964</t>
+          <t>26760</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18404</t>
+          <t>18918</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39917</t>
+          <t>40171</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31219</t>
+          <t>31792</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60453</t>
+          <t>59434</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31311</t>
+          <t>30972</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58507</t>
+          <t>57256</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>61461</t>
+          <t>58472</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>93593</t>
+          <t>93610</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>97447</t>
+          <t>96669</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>140018</t>
+          <t>140238</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>172905</t>
+          <t>174351</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>222975</t>
+          <t>225415</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>216340</t>
+          <t>218076</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>274238</t>
+          <t>276674</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>409189</t>
+          <t>404662</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>485368</t>
+          <t>487288</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197441</t>
+          <t>192439</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>252925</t>
+          <t>251634</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>264872</t>
+          <t>263524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>327408</t>
+          <t>324886</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>478094</t>
+          <t>473474</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>557168</t>
+          <t>562057</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>737708</t>
+          <t>742971</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>822801</t>
+          <t>822986</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>592187</t>
+          <t>596946</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>673819</t>
+          <t>675870</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1355050</t>
+          <t>1350404</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1470748</t>
+          <t>1469340</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,78%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>398574</t>
+          <t>399763</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>472566</t>
+          <t>474100</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>281389</t>
+          <t>279198</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>345933</t>
+          <t>345482</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>692411</t>
+          <t>693362</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>794238</t>
+          <t>796902</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>906</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7762</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17470</t>
+          <t>18227</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20893</t>
+          <t>23082</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25897</t>
+          <t>25496</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>11981</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31045</t>
+          <t>30852</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26704</t>
+          <t>26079</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50226</t>
+          <t>51232</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50956</t>
+          <t>51299</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>81997</t>
+          <t>80880</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56417</t>
+          <t>56403</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>87275</t>
+          <t>87161</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>114603</t>
+          <t>114396</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>159023</t>
+          <t>160345</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>56009</t>
+          <t>58281</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>87668</t>
+          <t>89925</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56607</t>
+          <t>56840</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>88259</t>
+          <t>90395</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>120404</t>
+          <t>121502</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>166481</t>
+          <t>166802</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>206560</t>
+          <t>209505</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>257010</t>
+          <t>256499</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>183950</t>
+          <t>185114</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>228503</t>
+          <t>229281</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>402675</t>
+          <t>407331</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>471568</t>
+          <t>471580</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>141990</t>
+          <t>141062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>187039</t>
+          <t>187169</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>80904</t>
+          <t>81291</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>116196</t>
+          <t>115215</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>233257</t>
+          <t>230745</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>291428</t>
+          <t>288886</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14756</t>
+          <t>14453</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35502</t>
+          <t>34838</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37982</t>
+          <t>36834</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67272</t>
+          <t>66569</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>57798</t>
+          <t>57414</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94372</t>
+          <t>94730</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>85030</t>
+          <t>86128</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>123660</t>
+          <t>124083</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>139606</t>
+          <t>141007</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>187378</t>
+          <t>190842</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>234413</t>
+          <t>238422</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>301087</t>
+          <t>301631</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>413626</t>
+          <t>409965</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>492602</t>
+          <t>492044</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>551631</t>
+          <t>549045</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>638438</t>
+          <t>638603</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>981818</t>
+          <t>983556</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1102515</t>
+          <t>1104715</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>382286</t>
+          <t>379710</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>457304</t>
+          <t>458826</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>546365</t>
+          <t>548050</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>642511</t>
+          <t>634698</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>951250</t>
+          <t>949616</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1069072</t>
+          <t>1065844</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,01%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1349338</t>
+          <t>1346753</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1457244</t>
+          <t>1464929</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1275237</t>
+          <t>1284648</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1396899</t>
+          <t>1396985</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2662085</t>
+          <t>2662730</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2830429</t>
+          <t>2825168</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,45%</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>826475</t>
+          <t>828284</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>928769</t>
+          <t>927089</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>594322</t>
+          <t>595587</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>688455</t>
+          <t>688713</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1447643</t>
+          <t>1450304</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1591764</t>
+          <t>1592559</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16588</t>
+          <t>16239</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37759</t>
+          <t>37461</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42970</t>
+          <t>44529</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76247</t>
+          <t>74717</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63783</t>
+          <t>65810</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101365</t>
+          <t>101609</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31465</t>
+          <t>32198</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57746</t>
+          <t>59142</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62470</t>
+          <t>60039</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97191</t>
+          <t>94786</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100662</t>
+          <t>100188</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>143961</t>
+          <t>145433</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>116906</t>
+          <t>115502</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>161656</t>
+          <t>162290</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313787</t>
+          <t>313741</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>381607</t>
+          <t>379234</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>443477</t>
+          <t>446705</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>525564</t>
+          <t>527170</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103191</t>
+          <t>105501</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>149656</t>
+          <t>148964</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136116</t>
+          <t>137143</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>184348</t>
+          <t>186373</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4533,47 +4533,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
+          <t>13,95%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>284452</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>254373</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>318637</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>12,32%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>11,02%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>13,8%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>284452</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>252855</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>316982</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>12,32%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>10,95%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4596,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>265510</t>
+          <t>268526</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>326628</t>
+          <t>324981</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>375746</t>
+          <t>373719</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>443287</t>
+          <t>443086</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>661253</t>
+          <t>658145</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>749892</t>
+          <t>749185</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>316112</t>
+          <t>316266</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>378885</t>
+          <t>376951</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>254673</t>
+          <t>252950</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>314565</t>
+          <t>316185</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>584548</t>
+          <t>585435</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>676790</t>
+          <t>674355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,21%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28046</t>
+          <t>27375</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52105</t>
+          <t>52490</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51433</t>
+          <t>50810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85403</t>
+          <t>84989</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86696</t>
+          <t>82689</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>129667</t>
+          <t>125808</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36266</t>
+          <t>35421</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61593</t>
+          <t>63634</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53136</t>
+          <t>51603</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87655</t>
+          <t>86402</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>94934</t>
+          <t>93702</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>137118</t>
+          <t>137524</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>215270</t>
+          <t>214985</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>277964</t>
+          <t>279294</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>319039</t>
+          <t>317071</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>391803</t>
+          <t>385009</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>553882</t>
+          <t>555167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>643753</t>
+          <t>654369</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>220390</t>
+          <t>221780</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>283532</t>
+          <t>281599</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>222817</t>
+          <t>219547</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>281381</t>
+          <t>280655</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>464500</t>
+          <t>459519</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>548799</t>
+          <t>546859</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>594889</t>
+          <t>594837</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>682977</t>
+          <t>685953</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>424268</t>
+          <t>420393</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>499630</t>
+          <t>496294</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1046696</t>
+          <t>1048087</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1164655</t>
+          <t>1162102</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>697762</t>
+          <t>696993</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>785125</t>
+          <t>789130</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>517583</t>
+          <t>517557</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>597738</t>
+          <t>602445</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1235050</t>
+          <t>1229187</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1353667</t>
+          <t>1352226</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,39%</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21550</t>
+          <t>20572</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10753</t>
+          <t>11060</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27473</t>
+          <t>28757</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>2364</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>17913</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27840</t>
+          <t>28096</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15555</t>
+          <t>15644</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37475</t>
+          <t>37540</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5960,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41610</t>
+          <t>41028</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>72668</t>
+          <t>72222</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44866</t>
+          <t>43920</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73862</t>
+          <t>72566</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94349</t>
+          <t>94040</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>136737</t>
+          <t>137812</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55954</t>
+          <t>56089</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>90122</t>
+          <t>89925</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>42907</t>
+          <t>42652</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>71251</t>
+          <t>71548</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>105220</t>
+          <t>104336</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>149674</t>
+          <t>150384</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,02%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>127247</t>
+          <t>127381</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>171980</t>
+          <t>168738</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>132819</t>
+          <t>133733</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>173179</t>
+          <t>175683</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>271873</t>
+          <t>269656</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>332243</t>
+          <t>328410</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>34,98%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>170112</t>
+          <t>171210</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>215425</t>
+          <t>216906</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>140387</t>
+          <t>139925</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>183784</t>
+          <t>184342</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>325007</t>
+          <t>325379</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>386400</t>
+          <t>387064</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,23%</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>55085</t>
+          <t>54995</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>88952</t>
+          <t>87788</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>112329</t>
+          <t>113923</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>161229</t>
+          <t>163343</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>178239</t>
+          <t>178443</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>233845</t>
+          <t>234624</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>81563</t>
+          <t>80915</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>122182</t>
+          <t>120525</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>137850</t>
+          <t>137878</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>187733</t>
+          <t>190792</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>231020</t>
+          <t>234215</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>295430</t>
+          <t>295934</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>400189</t>
+          <t>402409</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>485059</t>
+          <t>482854</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>702754</t>
+          <t>709002</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>810532</t>
+          <t>807946</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1138913</t>
+          <t>1134426</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1264390</t>
+          <t>1261015</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,11%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>409383</t>
+          <t>411552</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>488368</t>
+          <t>489381</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>424021</t>
+          <t>428161</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>510971</t>
+          <t>511031</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>858209</t>
+          <t>860101</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>973693</t>
+          <t>978327</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1027154</t>
+          <t>1027008</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1139441</t>
+          <t>1140728</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>970165</t>
+          <t>968095</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1075466</t>
+          <t>1077812</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2028316</t>
+          <t>2033492</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2181781</t>
+          <t>2182175</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1213536</t>
+          <t>1218295</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1336695</t>
+          <t>1334903</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>947633</t>
+          <t>942702</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1057332</t>
+          <t>1060105</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2189128</t>
+          <t>2192698</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2353710</t>
+          <t>2361616</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17345</t>
+          <t>17456</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21529</t>
+          <t>21692</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45998</t>
+          <t>44441</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30196</t>
+          <t>30902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55736</t>
+          <t>56084</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -7668,12 +7668,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16215</t>
+          <t>16148</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35050</t>
+          <t>35086</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42138</t>
+          <t>39907</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73146</t>
+          <t>70820</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61236</t>
+          <t>60700</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97948</t>
+          <t>98589</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -7781,12 +7781,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>101751</t>
+          <t>101245</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>142134</t>
+          <t>138920</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>170264</t>
+          <t>171060</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>223579</t>
+          <t>220550</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>285719</t>
+          <t>284614</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>349743</t>
+          <t>349711</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>135885</t>
+          <t>136743</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>178589</t>
+          <t>178605</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7929,12 +7929,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>196291</t>
+          <t>199231</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>252616</t>
+          <t>255826</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7964,12 +7964,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>349295</t>
+          <t>348546</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>418469</t>
+          <t>417746</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>201127</t>
+          <t>202094</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>248095</t>
+          <t>250825</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8022,12 +8022,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>233219</t>
+          <t>233933</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>294390</t>
+          <t>292860</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>448765</t>
+          <t>449217</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>522586</t>
+          <t>528452</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -8120,12 +8120,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>197720</t>
+          <t>193645</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>245770</t>
+          <t>243433</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>197526</t>
+          <t>198004</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>251540</t>
+          <t>254715</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>403968</t>
+          <t>408094</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>479437</t>
+          <t>479449</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17157</t>
+          <t>17011</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38778</t>
+          <t>39282</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8385,12 +8385,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31083</t>
+          <t>30389</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55850</t>
+          <t>57923</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53524</t>
+          <t>51703</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>87815</t>
+          <t>85645</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -8463,12 +8463,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17219</t>
+          <t>17058</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39485</t>
+          <t>39056</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39175</t>
+          <t>38835</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67465</t>
+          <t>68128</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>60222</t>
+          <t>60817</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>97129</t>
+          <t>98170</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -8576,12 +8576,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>147882</t>
+          <t>147521</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>199892</t>
+          <t>201033</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>183498</t>
+          <t>185311</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>236576</t>
+          <t>241132</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>346232</t>
+          <t>345587</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>421790</t>
+          <t>421345</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -8689,12 +8689,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>268707</t>
+          <t>266747</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>332324</t>
+          <t>331823</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>293191</t>
+          <t>289767</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>359932</t>
+          <t>359222</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>577003</t>
+          <t>576831</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>672889</t>
+          <t>671086</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>651859</t>
+          <t>647447</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>738114</t>
+          <t>735562</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>588612</t>
+          <t>589499</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>675195</t>
+          <t>675047</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1259810</t>
+          <t>1263808</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1382427</t>
+          <t>1382513</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -8915,12 +8915,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>814062</t>
+          <t>807793</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>906591</t>
+          <t>907186</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8930,12 +8930,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8950,12 +8950,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>680867</t>
+          <t>684784</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>772045</t>
+          <t>772456</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1528875</t>
+          <t>1519535</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1649012</t>
+          <t>1648049</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9000,12 +9000,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,59%</t>
         </is>
       </c>
     </row>
@@ -9145,12 +9145,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8407</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10021</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14449</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -9258,12 +9258,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17390</t>
+          <t>16737</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5084</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19679</t>
+          <t>21166</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11756</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32901</t>
+          <t>32611</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -9371,12 +9371,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29784</t>
+          <t>30477</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56099</t>
+          <t>56895</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9386,12 +9386,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50867</t>
+          <t>49122</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>80298</t>
+          <t>79253</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9421,12 +9421,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86844</t>
+          <t>86889</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>125293</t>
+          <t>126279</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -9484,12 +9484,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58163</t>
+          <t>56340</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>89495</t>
+          <t>87239</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9499,12 +9499,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>70487</t>
+          <t>70199</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>105159</t>
+          <t>105499</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9534,12 +9534,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9554,12 +9554,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137907</t>
+          <t>136221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>185637</t>
+          <t>182146</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9569,12 +9569,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>169780</t>
+          <t>170312</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>215872</t>
+          <t>219225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>166081</t>
+          <t>167391</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>210966</t>
+          <t>214552</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9647,12 +9647,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>349362</t>
+          <t>350283</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>415058</t>
+          <t>414019</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,84%</t>
         </is>
       </c>
     </row>
@@ -9710,12 +9710,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>205430</t>
+          <t>204447</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>253210</t>
+          <t>253122</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9725,12 +9725,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>171205</t>
+          <t>168814</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>216684</t>
+          <t>213066</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>390118</t>
+          <t>389479</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>452027</t>
+          <t>454975</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,59%</t>
         </is>
       </c>
     </row>
@@ -9940,12 +9940,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27891</t>
+          <t>27990</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>52665</t>
+          <t>53180</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60067</t>
+          <t>61266</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>96976</t>
+          <t>97934</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9990,12 +9990,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>97015</t>
+          <t>93545</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>144072</t>
+          <t>140070</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -10053,12 +10053,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>45157</t>
+          <t>44577</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>77256</t>
+          <t>76905</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>99063</t>
+          <t>93989</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>142588</t>
+          <t>142153</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>151438</t>
+          <t>150892</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>208060</t>
+          <t>205080</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -10166,12 +10166,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>298438</t>
+          <t>298450</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>368128</t>
+          <t>368185</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>430359</t>
+          <t>431625</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>513290</t>
+          <t>515679</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10216,12 +10216,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>754042</t>
+          <t>752882</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>859417</t>
+          <t>861460</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -10279,12 +10279,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>485455</t>
+          <t>484859</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>570468</t>
+          <t>568032</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>590072</t>
+          <t>590019</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>686335</t>
+          <t>682218</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1097735</t>
+          <t>1102916</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1224204</t>
+          <t>1232586</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1051154</t>
+          <t>1052557</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1164201</t>
+          <t>1167396</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1025659</t>
+          <t>1017298</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1132216</t>
+          <t>1137327</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10442,12 +10442,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2117904</t>
+          <t>2112707</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2273673</t>
+          <t>2274917</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,96%</t>
         </is>
       </c>
     </row>
@@ -10505,12 +10505,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1245768</t>
+          <t>1249446</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1361592</t>
+          <t>1365566</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10540,12 +10540,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1088863</t>
+          <t>1084857</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1204990</t>
+          <t>1198299</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10555,12 +10555,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10575,12 +10575,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2373543</t>
+          <t>2373094</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2531576</t>
+          <t>2539449</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10595,7 +10595,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,8%</t>
         </is>
       </c>
     </row>
@@ -10961,22 +10961,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9264</t>
+          <t>9812</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15547</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10996,32 +10996,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18114</t>
+          <t>19825</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12641</t>
+          <t>13935</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24578</t>
+          <t>27234</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11031,32 +11031,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>27378</t>
+          <t>29637</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20155</t>
+          <t>22691</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35228</t>
+          <t>38540</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -11074,32 +11074,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23300</t>
+          <t>24854</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15530</t>
+          <t>16431</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33822</t>
+          <t>35733</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11109,32 +11109,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>59945</t>
+          <t>66103</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49975</t>
+          <t>53681</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71798</t>
+          <t>78040</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11144,32 +11144,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>83245</t>
+          <t>90956</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68998</t>
+          <t>76480</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98119</t>
+          <t>107672</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -11187,32 +11187,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>68638</t>
+          <t>73687</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56215</t>
+          <t>60705</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>83145</t>
+          <t>89189</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11222,32 +11222,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>137688</t>
+          <t>150562</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>123006</t>
+          <t>133740</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>154095</t>
+          <t>168218</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11257,32 +11257,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>206325</t>
+          <t>224249</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>184187</t>
+          <t>202000</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>226365</t>
+          <t>246806</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -11300,32 +11300,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>97009</t>
+          <t>100892</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81241</t>
+          <t>83900</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115361</t>
+          <t>118442</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11335,32 +11335,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>149603</t>
+          <t>164247</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>133639</t>
+          <t>147804</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>165781</t>
+          <t>183853</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11370,32 +11370,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>246612</t>
+          <t>265138</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>224430</t>
+          <t>241033</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>268620</t>
+          <t>290316</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -11413,22 +11413,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>157933</t>
+          <t>176569</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>139039</t>
+          <t>156191</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>178821</t>
+          <t>198538</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11448,32 +11448,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>212760</t>
+          <t>224894</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193029</t>
+          <t>205288</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>232532</t>
+          <t>244466</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11483,32 +11483,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>370693</t>
+          <t>401463</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>342955</t>
+          <t>372634</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>395862</t>
+          <t>432615</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -11526,32 +11526,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>157980</t>
+          <t>191849</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>140754</t>
+          <t>167793</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>177867</t>
+          <t>216607</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11561,32 +11561,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>177398</t>
+          <t>196408</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>159507</t>
+          <t>177538</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>198221</t>
+          <t>218449</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11596,32 +11596,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>335378</t>
+          <t>388257</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>310273</t>
+          <t>357955</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>363241</t>
+          <t>416518</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -11639,17 +11639,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>514123</t>
+          <t>577662</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>514123</t>
+          <t>577662</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>514123</t>
+          <t>577662</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11674,17 +11674,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11709,17 +11709,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1269631</t>
+          <t>1399700</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1269631</t>
+          <t>1399700</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1269631</t>
+          <t>1399700</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11756,32 +11756,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>20259</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10257</t>
+          <t>12407</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29009</t>
+          <t>32702</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11791,32 +11791,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37731</t>
+          <t>40843</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26160</t>
+          <t>30155</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55928</t>
+          <t>56198</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11826,32 +11826,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>55944</t>
+          <t>61102</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40791</t>
+          <t>47677</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76326</t>
+          <t>78988</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -11869,32 +11869,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>63989</t>
+          <t>69304</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40325</t>
+          <t>52843</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>85956</t>
+          <t>90289</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11904,32 +11904,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>288993</t>
+          <t>92421</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>87233</t>
+          <t>77483</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>756755</t>
+          <t>112969</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11939,32 +11939,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>352982</t>
+          <t>161725</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>145962</t>
+          <t>140589</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1015459</t>
+          <t>193324</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -11982,32 +11982,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>193015</t>
+          <t>206845</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>133778</t>
+          <t>179409</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>230777</t>
+          <t>242017</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12017,32 +12017,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>256003</t>
+          <t>288308</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>192589</t>
+          <t>263989</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>302877</t>
+          <t>317229</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12052,32 +12052,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>449018</t>
+          <t>495152</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>366878</t>
+          <t>457558</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>512160</t>
+          <t>539420</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -12095,32 +12095,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>235873</t>
+          <t>265305</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>159656</t>
+          <t>237754</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>280452</t>
+          <t>301685</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12130,32 +12130,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>234849</t>
+          <t>265177</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>175777</t>
+          <t>239889</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>272938</t>
+          <t>293247</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12165,32 +12165,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>470723</t>
+          <t>530482</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>382838</t>
+          <t>492616</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>539484</t>
+          <t>574846</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -12208,32 +12208,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>645533</t>
+          <t>689536</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>449464</t>
+          <t>638472</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>741189</t>
+          <t>744420</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12243,32 +12243,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>584767</t>
+          <t>647415</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>439376</t>
+          <t>609762</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>674173</t>
+          <t>686554</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12278,32 +12278,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1230300</t>
+          <t>1336952</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>996582</t>
+          <t>1279756</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1379334</t>
+          <t>1404473</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -12321,32 +12321,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1133704</t>
+          <t>979316</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>972119</t>
+          <t>921518</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1516393</t>
+          <t>1033687</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12356,32 +12356,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>834480</t>
+          <t>836195</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>624583</t>
+          <t>791104</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>969742</t>
+          <t>877568</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12391,32 +12391,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1968184</t>
+          <t>1815511</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1716156</t>
+          <t>1752777</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2400045</t>
+          <t>1887494</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>42,89%</t>
         </is>
       </c>
     </row>
@@ -12434,17 +12434,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12469,17 +12469,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2236824</t>
+          <t>2170358</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2236824</t>
+          <t>2170358</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2236824</t>
+          <t>2170358</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12504,17 +12504,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4527151</t>
+          <t>4400924</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4527151</t>
+          <t>4400924</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4527151</t>
+          <t>4400924</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12551,32 +12551,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14115</t>
+          <t>14222</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12586,32 +12586,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>14423</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6598</t>
+          <t>8783</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18241</t>
+          <t>22216</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12621,27 +12621,27 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>18439</t>
+          <t>21483</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>13868</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27882</t>
+          <t>30834</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -12664,32 +12664,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17545</t>
+          <t>18220</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>10278</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29764</t>
+          <t>28451</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12699,32 +12699,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25259</t>
+          <t>26766</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18430</t>
+          <t>19213</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35740</t>
+          <t>36159</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12734,32 +12734,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>42804</t>
+          <t>44986</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32931</t>
+          <t>34577</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55767</t>
+          <t>58137</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -12777,32 +12777,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>67324</t>
+          <t>77890</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52277</t>
+          <t>61914</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>85741</t>
+          <t>95424</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12812,32 +12812,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>89979</t>
+          <t>102711</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>75049</t>
+          <t>88078</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>106913</t>
+          <t>119508</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12847,32 +12847,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>157303</t>
+          <t>180602</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>135358</t>
+          <t>157774</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>180893</t>
+          <t>206302</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -12890,32 +12890,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>78940</t>
+          <t>86365</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>61929</t>
+          <t>69759</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>97227</t>
+          <t>106534</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12925,32 +12925,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>87097</t>
+          <t>96751</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>74479</t>
+          <t>82503</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>105583</t>
+          <t>113331</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12960,32 +12960,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>166037</t>
+          <t>183115</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>143578</t>
+          <t>160765</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>189929</t>
+          <t>208935</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -13003,32 +13003,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>195402</t>
+          <t>219663</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>170315</t>
+          <t>195927</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>218751</t>
+          <t>248824</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13038,32 +13038,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>226132</t>
+          <t>251522</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>205557</t>
+          <t>228401</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>247556</t>
+          <t>275925</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13073,32 +13073,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>421534</t>
+          <t>471185</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>391681</t>
+          <t>438900</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>457762</t>
+          <t>505126</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -13116,32 +13116,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>280408</t>
+          <t>302388</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>253746</t>
+          <t>272839</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>310614</t>
+          <t>330975</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13151,32 +13151,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>220560</t>
+          <t>242704</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>198055</t>
+          <t>218547</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>243449</t>
+          <t>267617</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13186,32 +13186,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>500968</t>
+          <t>545093</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>464078</t>
+          <t>507264</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>537464</t>
+          <t>582545</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>40,27%</t>
         </is>
       </c>
     </row>
@@ -13229,17 +13229,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13264,17 +13264,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13299,17 +13299,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13346,32 +13346,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>34480</t>
+          <t>37132</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22781</t>
+          <t>27294</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47843</t>
+          <t>52454</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13381,32 +13381,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>67281</t>
+          <t>75090</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52557</t>
+          <t>62995</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>84639</t>
+          <t>92959</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13416,32 +13416,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>101761</t>
+          <t>112222</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>83651</t>
+          <t>94862</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>125149</t>
+          <t>134554</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -13459,32 +13459,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>104834</t>
+          <t>112379</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>79241</t>
+          <t>92265</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>129514</t>
+          <t>136896</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13494,32 +13494,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>374197</t>
+          <t>185289</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>172812</t>
+          <t>162236</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>971288</t>
+          <t>208861</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13529,32 +13529,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>479031</t>
+          <t>297667</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>267170</t>
+          <t>267329</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1195274</t>
+          <t>332726</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -13572,32 +13572,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>328977</t>
+          <t>358422</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>247485</t>
+          <t>326857</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>372629</t>
+          <t>397826</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13607,32 +13607,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>483670</t>
+          <t>541581</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>393394</t>
+          <t>502538</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>534154</t>
+          <t>579245</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -13642,32 +13642,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>812647</t>
+          <t>900003</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>712668</t>
+          <t>849532</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>879586</t>
+          <t>955980</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -13685,32 +13685,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>411822</t>
+          <t>452562</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>322849</t>
+          <t>415456</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>463268</t>
+          <t>496735</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13720,67 +13720,67 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>471550</t>
+          <t>526174</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>392059</t>
+          <t>489967</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>520655</t>
+          <t>565020</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
+          <t>15,16%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>1322</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>978736</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>925493</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>1032968</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>13,51%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>12,77%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>14,25%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>1322</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>883372</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>765639</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>958082</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>12,44%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>10,78%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -13798,32 +13798,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>998868</t>
+          <t>1085768</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>750998</t>
+          <t>1027728</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1096088</t>
+          <t>1154262</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13833,32 +13833,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1023659</t>
+          <t>1123832</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>842125</t>
+          <t>1074632</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1112819</t>
+          <t>1172557</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13868,32 +13868,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2022527</t>
+          <t>2209600</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1754197</t>
+          <t>2136507</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2168179</t>
+          <t>2289789</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -13911,32 +13911,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1572092</t>
+          <t>1473554</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1410324</t>
+          <t>1405656</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2051162</t>
+          <t>1537996</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13946,32 +13946,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1232438</t>
+          <t>1275307</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1043009</t>
+          <t>1224146</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1376010</t>
+          <t>1330515</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13981,32 +13981,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2804531</t>
+          <t>2748861</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2551513</t>
+          <t>2660621</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3254462</t>
+          <t>2835355</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>39,12%</t>
         </is>
       </c>
     </row>
@@ -14024,17 +14024,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3451073</t>
+          <t>3519816</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3451073</t>
+          <t>3519816</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3451073</t>
+          <t>3519816</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14059,17 +14059,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3652795</t>
+          <t>3727273</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3652795</t>
+          <t>3727273</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3652795</t>
+          <t>3727273</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14094,17 +14094,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>7103869</t>
+          <t>7247089</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7103869</t>
+          <t>7247089</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7103869</t>
+          <t>7247089</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
